--- a/ig/PreparerPubli-101Ballot/all-profiles.xlsx
+++ b/ig/PreparerPubli-101Ballot/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0-ballot</t>
+    <t>1.0.1-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T16:56:13+00:00</t>
+    <t>2024-02-13T09:36:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
